--- a/image processing/chapter4.xlsx
+++ b/image processing/chapter4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D 資料匣\課程\勤益課程\數位影像\PPT\授課版_(教師專用)\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D 資料匣\課程\勤益課程\數位影像\image processing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03DB2D9-B34F-4BEF-9F94-AB3B84264F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98357882-BD71-4A13-BEDE-979D6AD08518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="583" windowWidth="24686" windowHeight="13131" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35760" yWindow="-3440" windowWidth="28800" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="238">
   <si>
     <t>question</t>
   </si>
@@ -38,624 +38,6 @@
   </si>
   <si>
     <t>answer</t>
-  </si>
-  <si>
-    <t>像素變換屬於哪種影像處理方式？</t>
-  </si>
-  <si>
-    <t>空間域處理</t>
-  </si>
-  <si>
-    <t>形態學處理</t>
-  </si>
-  <si>
-    <t>頻率域處理</t>
-  </si>
-  <si>
-    <t>幾何變換</t>
-  </si>
-  <si>
-    <t>點運算的特點是？</t>
-  </si>
-  <si>
-    <t>需要鄰域資訊</t>
-  </si>
-  <si>
-    <t>需要全域資訊</t>
-  </si>
-  <si>
-    <t>需要多張影像</t>
-  </si>
-  <si>
-    <t>只處理單一像素</t>
-  </si>
-  <si>
-    <t>影像負片的數學運算是？</t>
-  </si>
-  <si>
-    <t>s = r + 255</t>
-  </si>
-  <si>
-    <t>s = r * 2</t>
-  </si>
-  <si>
-    <t>s = 255 - r</t>
-  </si>
-  <si>
-    <t>s = r / 2</t>
-  </si>
-  <si>
-    <t>對數轉換的主要用途是？</t>
-  </si>
-  <si>
-    <t>壓縮高灰度值</t>
-  </si>
-  <si>
-    <t>同時壓縮高值和擴展低值</t>
-  </si>
-  <si>
-    <t>反轉影像</t>
-  </si>
-  <si>
-    <t>擴展低灰度值</t>
-  </si>
-  <si>
-    <t>伽瑪轉換的公式是？</t>
-  </si>
-  <si>
-    <t>s = c + r</t>
-  </si>
-  <si>
-    <t>s = c - r</t>
-  </si>
-  <si>
-    <t>s = c * r^γ</t>
-  </si>
-  <si>
-    <t>s = c * r</t>
-  </si>
-  <si>
-    <t>當γ &lt; 1時，伽瑪轉換會？</t>
-  </si>
-  <si>
-    <t>使影像變亮</t>
-  </si>
-  <si>
-    <t>使影像變暗</t>
-  </si>
-  <si>
-    <t>不改變影像</t>
-  </si>
-  <si>
-    <t>當γ &gt; 1時，伽瑪轉換會？</t>
-  </si>
-  <si>
-    <t>對比度拉伸的目的是？</t>
-  </si>
-  <si>
-    <t>壓縮灰度範圍</t>
-  </si>
-  <si>
-    <t>擴展灰度範圍</t>
-  </si>
-  <si>
-    <t>反轉灰度</t>
-  </si>
-  <si>
-    <t>均化灰度</t>
-  </si>
-  <si>
-    <t>灰度切割的主要應用是？</t>
-  </si>
-  <si>
-    <t>去除雜訊</t>
-  </si>
-  <si>
-    <t>銳化邊緣</t>
-  </si>
-  <si>
-    <t>突出特定灰度範圍</t>
-  </si>
-  <si>
-    <t>增強整體對比</t>
-  </si>
-  <si>
-    <t>位元平面切割可以用於？</t>
-  </si>
-  <si>
-    <t>色彩轉換</t>
-  </si>
-  <si>
-    <t>邊緣檢測</t>
-  </si>
-  <si>
-    <t>影像壓縮和分析</t>
-  </si>
-  <si>
-    <t>影像旋轉</t>
-  </si>
-  <si>
-    <t>最高位元平面包含影像的？</t>
-  </si>
-  <si>
-    <t>細節資訊</t>
-  </si>
-  <si>
-    <t>色彩資訊</t>
-  </si>
-  <si>
-    <t>雜訊資訊</t>
-  </si>
-  <si>
-    <t>主要視覺資訊</t>
-  </si>
-  <si>
-    <t>最低位元平面通常包含？</t>
-  </si>
-  <si>
-    <t>邊緣資訊</t>
-  </si>
-  <si>
-    <t>紋理資訊</t>
-  </si>
-  <si>
-    <t>主要資訊</t>
-  </si>
-  <si>
-    <t>雜訊和細微變化</t>
-  </si>
-  <si>
-    <t>直方圖表示影像的？</t>
-  </si>
-  <si>
-    <t>灰度分布</t>
-  </si>
-  <si>
-    <t>空間分布</t>
-  </si>
-  <si>
-    <t>頻率分布</t>
-  </si>
-  <si>
-    <t>色彩分布</t>
-  </si>
-  <si>
-    <t>直方圖的橫軸代表？</t>
-  </si>
-  <si>
-    <t>像素數量</t>
-  </si>
-  <si>
-    <t>對比度</t>
-  </si>
-  <si>
-    <t>影像大小</t>
-  </si>
-  <si>
-    <t>灰度值</t>
-  </si>
-  <si>
-    <t>直方圖的縱軸代表？</t>
-  </si>
-  <si>
-    <t>亮度</t>
-  </si>
-  <si>
-    <t>直方圖均化的目的是？</t>
-  </si>
-  <si>
-    <t>增強對比度</t>
-  </si>
-  <si>
-    <t>壓縮對比度</t>
-  </si>
-  <si>
-    <t>銳化影像</t>
-  </si>
-  <si>
-    <t>直方圖均化後的直方圖趨向於？</t>
-  </si>
-  <si>
-    <t>集中分布</t>
-  </si>
-  <si>
-    <t>正態分布</t>
-  </si>
-  <si>
-    <t>雙峰分布</t>
-  </si>
-  <si>
-    <t>均勻分布</t>
-  </si>
-  <si>
-    <t>直方圖匹配的目的是？</t>
-  </si>
-  <si>
-    <t>使直方圖符合指定形狀</t>
-  </si>
-  <si>
-    <t>壓縮直方圖</t>
-  </si>
-  <si>
-    <t>反轉直方圖</t>
-  </si>
-  <si>
-    <t>均化直方圖</t>
-  </si>
-  <si>
-    <t>局部直方圖均化用於？</t>
-  </si>
-  <si>
-    <t>雜訊去除</t>
-  </si>
-  <si>
-    <t>局部增強</t>
-  </si>
-  <si>
-    <t>全域增強</t>
-  </si>
-  <si>
-    <t>累積分布函數（CDF）用於？</t>
-  </si>
-  <si>
-    <t>影像壓縮</t>
-  </si>
-  <si>
-    <t>濾波處理</t>
-  </si>
-  <si>
-    <t>直方圖均化</t>
-  </si>
-  <si>
-    <t>線性變換的形式是？</t>
-  </si>
-  <si>
-    <t>s = a * r^2</t>
-  </si>
-  <si>
-    <t>s = log(r)</t>
-  </si>
-  <si>
-    <t>s = ar + b</t>
-  </si>
-  <si>
-    <t>s = e^r</t>
-  </si>
-  <si>
-    <t>分段線性變換可以實現？</t>
-  </si>
-  <si>
-    <t>只能壓縮對比</t>
-  </si>
-  <si>
-    <t>靈活控制不同灰度範圍</t>
-  </si>
-  <si>
-    <t>只能反轉影像</t>
-  </si>
-  <si>
-    <t>只能增強對比</t>
-  </si>
-  <si>
-    <t>閾值處理會產生？</t>
-  </si>
-  <si>
-    <t>二值影像</t>
-  </si>
-  <si>
-    <t>負片影像</t>
-  </si>
-  <si>
-    <t>灰階影像</t>
-  </si>
-  <si>
-    <t>彩色影像</t>
-  </si>
-  <si>
-    <t>全域閾值的缺點是？</t>
-  </si>
-  <si>
-    <t>計算複雜</t>
-  </si>
-  <si>
-    <t>記憶體需求大</t>
-  </si>
-  <si>
-    <t>處理速度慢</t>
-  </si>
-  <si>
-    <t>不適合光照不均的影像</t>
-  </si>
-  <si>
-    <t>自適應閾值的優點是？</t>
-  </si>
-  <si>
-    <t>速度最快</t>
-  </si>
-  <si>
-    <t>適應局部變化</t>
-  </si>
-  <si>
-    <t>記憶體最少</t>
-  </si>
-  <si>
-    <t>計算簡單</t>
-  </si>
-  <si>
-    <t>Otsu方法是一種？</t>
-  </si>
-  <si>
-    <t>自動閾值選擇</t>
-  </si>
-  <si>
-    <t>多閾值方法</t>
-  </si>
-  <si>
-    <t>局部閾值</t>
-  </si>
-  <si>
-    <t>手動閾值選擇</t>
-  </si>
-  <si>
-    <t>Otsu方法的原理是？</t>
-  </si>
-  <si>
-    <t>最大化類間變異</t>
-  </si>
-  <si>
-    <t>平均灰度值</t>
-  </si>
-  <si>
-    <t>中值灰度值</t>
-  </si>
-  <si>
-    <t>最小化類內變異</t>
-  </si>
-  <si>
-    <t>對比度的定義是？</t>
-  </si>
-  <si>
-    <t>最大灰度值</t>
-  </si>
-  <si>
-    <t>最小灰度值</t>
-  </si>
-  <si>
-    <t>灰度值的範圍</t>
-  </si>
-  <si>
-    <t>低對比度影像的特徵是？</t>
-  </si>
-  <si>
-    <t>灰度範圍寬</t>
-  </si>
-  <si>
-    <t>只有黑白</t>
-  </si>
-  <si>
-    <t>灰度範圍窄</t>
-  </si>
-  <si>
-    <t>色彩豐富</t>
-  </si>
-  <si>
-    <t>高對比度影像的特徵是？</t>
-  </si>
-  <si>
-    <t>沒有細節</t>
-  </si>
-  <si>
-    <t>灰度集中</t>
-  </si>
-  <si>
-    <t>灰度分散</t>
-  </si>
-  <si>
-    <t>全部為灰色</t>
-  </si>
-  <si>
-    <t>影像的亮度是指？</t>
-  </si>
-  <si>
-    <t>灰度範圍</t>
-  </si>
-  <si>
-    <t>增加影像亮度的方法是？</t>
-  </si>
-  <si>
-    <t>所有像素除以常數</t>
-  </si>
-  <si>
-    <t>所有像素乘以常數</t>
-  </si>
-  <si>
-    <t>所有像素減去常數</t>
-  </si>
-  <si>
-    <t>所有像素加上常數</t>
-  </si>
-  <si>
-    <t>冪次轉換中，c是？</t>
-  </si>
-  <si>
-    <t>旋轉角度</t>
-  </si>
-  <si>
-    <t>指數參數</t>
-  </si>
-  <si>
-    <t>平移常數</t>
-  </si>
-  <si>
-    <t>縮放常數</t>
-  </si>
-  <si>
-    <t>反對數轉換用於？</t>
-  </si>
-  <si>
-    <t>旋轉影像</t>
-  </si>
-  <si>
-    <t>擴展動態範圍</t>
-  </si>
-  <si>
-    <t>壓縮動態範圍</t>
-  </si>
-  <si>
-    <t>影像的動態範圍是指？</t>
-  </si>
-  <si>
-    <t>像素總數</t>
-  </si>
-  <si>
-    <t>最大與最小灰度的比值</t>
-  </si>
-  <si>
-    <t>平均灰度</t>
-  </si>
-  <si>
-    <t>灰度總和</t>
-  </si>
-  <si>
-    <t>壓縮動態範圍的目的是？</t>
-  </si>
-  <si>
-    <t>減少解析度</t>
-  </si>
-  <si>
-    <t>增加雜訊</t>
-  </si>
-  <si>
-    <t>增加對比</t>
-  </si>
-  <si>
-    <t>便於顯示和儲存</t>
-  </si>
-  <si>
-    <t>直方圖規格化是指？</t>
-  </si>
-  <si>
-    <t>將直方圖映射到指定範圍</t>
-  </si>
-  <si>
-    <t>影像的飽和處理是指？</t>
-  </si>
-  <si>
-    <t>增加色彩飽和度</t>
-  </si>
-  <si>
-    <t>限制灰度值在有效範圍內</t>
-  </si>
-  <si>
-    <t>溢位處理通常採用？</t>
-  </si>
-  <si>
-    <t>中值</t>
-  </si>
-  <si>
-    <t>捨棄</t>
-  </si>
-  <si>
-    <t>飽和處理或取模</t>
-  </si>
-  <si>
-    <t>平均</t>
-  </si>
-  <si>
-    <t>影像相減可用於？</t>
-  </si>
-  <si>
-    <t>增強對比</t>
-  </si>
-  <si>
-    <t>運動檢測</t>
-  </si>
-  <si>
-    <t>影像相加可用於？</t>
-  </si>
-  <si>
-    <t>降低雜訊</t>
-  </si>
-  <si>
-    <t>影像分割</t>
-  </si>
-  <si>
-    <t>影像平均的主要用途是？</t>
-  </si>
-  <si>
-    <t>增強邊緣</t>
-  </si>
-  <si>
-    <t>降低隨機雜訊</t>
-  </si>
-  <si>
-    <t>影像相乘常用於？</t>
-  </si>
-  <si>
-    <t>遮罩操作</t>
-  </si>
-  <si>
-    <t>影像相除可用於？</t>
-  </si>
-  <si>
-    <t>校正光照不均</t>
-  </si>
-  <si>
-    <t>邏輯運算AND用於？</t>
-  </si>
-  <si>
-    <t>影像增強</t>
-  </si>
-  <si>
-    <t>提取重疊區域</t>
-  </si>
-  <si>
-    <t>邏輯運算OR用於？</t>
-  </si>
-  <si>
-    <t>提取交集</t>
-  </si>
-  <si>
-    <t>合併區域</t>
-  </si>
-  <si>
-    <t>邏輯運算NOT的效果等同於？</t>
-  </si>
-  <si>
-    <t>影像負片</t>
-  </si>
-  <si>
-    <t>模糊處理</t>
-  </si>
-  <si>
-    <t>對比增強</t>
-  </si>
-  <si>
-    <t>邏輯運算XOR可用於？</t>
-  </si>
-  <si>
-    <t>檢測差異</t>
-  </si>
-  <si>
-    <t>對比度受限的自適應直方圖均化（CLAHE）用於？</t>
-  </si>
-  <si>
-    <t>避免過度增強</t>
-  </si>
-  <si>
-    <t>查找表（LUT）的優點是？</t>
-  </si>
-  <si>
-    <t>提高精度</t>
-  </si>
-  <si>
-    <t>節省記憶體</t>
-  </si>
-  <si>
-    <t>減少雜訊</t>
-  </si>
-  <si>
-    <t>加快處理速度</t>
   </si>
   <si>
     <t>title</t>
@@ -668,7 +50,691 @@
     <t>chapter_name</t>
   </si>
   <si>
-    <t>CH 04 影像的像素變換</t>
+    <t>對比度</t>
+  </si>
+  <si>
+    <t>隨機選擇</t>
+  </si>
+  <si>
+    <t>在數位影像中，構成影像的最基本組成單位稱為什麼？</t>
+  </si>
+  <si>
+    <t>像素 (Pixel)</t>
+  </si>
+  <si>
+    <t>解析度 (Resolution)</t>
+  </si>
+  <si>
+    <t>張量 (Tensor)</t>
+  </si>
+  <si>
+    <t>矩陣 (Matrix)</t>
+  </si>
+  <si>
+    <t>對於8位元的灰階影像，每個像素的數值範圍為何？</t>
+  </si>
+  <si>
+    <t>0 到 128</t>
+  </si>
+  <si>
+    <t>1 到 256</t>
+  </si>
+  <si>
+    <t>0 到 255</t>
+  </si>
+  <si>
+    <t>0 到 100</t>
+  </si>
+  <si>
+    <t>在8位元灰階影像中，像素值為0代表什麼顏色？</t>
+  </si>
+  <si>
+    <t>完全白</t>
+  </si>
+  <si>
+    <t>灰色</t>
+  </si>
+  <si>
+    <t>完全黑</t>
+  </si>
+  <si>
+    <t>透明</t>
+  </si>
+  <si>
+    <t>在8位元灰階影像中，像素值為255代表什麼顏色？</t>
+  </si>
+  <si>
+    <t>中間灰</t>
+  </si>
+  <si>
+    <t>淺灰</t>
+  </si>
+  <si>
+    <t>RGB彩色影像模型是由哪三個顏色分量組成？</t>
+  </si>
+  <si>
+    <t>紅色、綠色、藍色</t>
+  </si>
+  <si>
+    <t>紅色、黃色、藍色</t>
+  </si>
+  <si>
+    <t>青色、洋紅、黃色</t>
+  </si>
+  <si>
+    <t>紅色、綠色、黑色</t>
+  </si>
+  <si>
+    <t>在RGB模型中，每個顏色分量的數值範圍為何？</t>
+  </si>
+  <si>
+    <t>1 到 255</t>
+  </si>
+  <si>
+    <t>RGB影像的三個矩陣組合起來稱為什麼？</t>
+  </si>
+  <si>
+    <t>向量 (Vector)</t>
+  </si>
+  <si>
+    <t>陣列 (Array)</t>
+  </si>
+  <si>
+    <t>序列 (Sequence)</t>
+  </si>
+  <si>
+    <t>灰度直方圖的英文名稱為何？</t>
+  </si>
+  <si>
+    <t>Gray Histogram</t>
+  </si>
+  <si>
+    <t>Gray Transform</t>
+  </si>
+  <si>
+    <t>Gray Scale</t>
+  </si>
+  <si>
+    <t>Gray Level</t>
+  </si>
+  <si>
+    <t>灰度直方圖主要用於描述影像中什麼資訊？</t>
+  </si>
+  <si>
+    <t>各灰度級別的像素分佈</t>
+  </si>
+  <si>
+    <t>影像的大小</t>
+  </si>
+  <si>
+    <t>影像的顏色</t>
+  </si>
+  <si>
+    <t>影像的格式</t>
+  </si>
+  <si>
+    <t>影像的解析度通常以什麼方式表示？</t>
+  </si>
+  <si>
+    <t>欄 (Column) 與列 (Row) 相乘</t>
+  </si>
+  <si>
+    <t>像素的總和</t>
+  </si>
+  <si>
+    <t>像素的平均值</t>
+  </si>
+  <si>
+    <t>顏色的數量</t>
+  </si>
+  <si>
+    <t>灰度線性變換的另一個常見名稱是什麼？</t>
+  </si>
+  <si>
+    <t>灰度拉伸</t>
+  </si>
+  <si>
+    <t>灰度壓縮</t>
+  </si>
+  <si>
+    <t>灰度反轉</t>
+  </si>
+  <si>
+    <t>灰度平滑</t>
+  </si>
+  <si>
+    <t>灰度線性變換主要用於改變影像的什麼特性？</t>
+  </si>
+  <si>
+    <t>大小</t>
+  </si>
+  <si>
+    <t>顏色</t>
+  </si>
+  <si>
+    <t>格式</t>
+  </si>
+  <si>
+    <t>在灰度線性變換公式 s = a × p + b 中，當 a &gt; 1 時會產生什麼效果？</t>
+  </si>
+  <si>
+    <t>對比度減少</t>
+  </si>
+  <si>
+    <t>影像變暗</t>
+  </si>
+  <si>
+    <t>對比度增加</t>
+  </si>
+  <si>
+    <t>影像模糊</t>
+  </si>
+  <si>
+    <t>在灰度線性變換公式 s = a × p + b 中，當 0 &lt; a &lt; 1 時會產生什麼效果？</t>
+  </si>
+  <si>
+    <t>影像變亮</t>
+  </si>
+  <si>
+    <t>影像銳化</t>
+  </si>
+  <si>
+    <t>在灰度線性變換公式 s = a × p + b 中，當 b 為正值時會產生什麼效果？</t>
+  </si>
+  <si>
+    <t>在灰度線性變換公式 s = a × p + b 中，當 b 為負值時會產生什麼效果？</t>
+  </si>
+  <si>
+    <t>灰度對數變換主要用於強調影像的哪個區域？</t>
+  </si>
+  <si>
+    <t>高強度區域</t>
+  </si>
+  <si>
+    <t>邊緣區域</t>
+  </si>
+  <si>
+    <t>中間強度區域</t>
+  </si>
+  <si>
+    <t>低強度區域</t>
+  </si>
+  <si>
+    <t>灰度對數變換可以有效增強影像的什麼細節？</t>
+  </si>
+  <si>
+    <t>亮部細節</t>
+  </si>
+  <si>
+    <t>顏色細節</t>
+  </si>
+  <si>
+    <t>邊緣細節</t>
+  </si>
+  <si>
+    <t>暗部細節</t>
+  </si>
+  <si>
+    <t>直方圖標準化的主要目的是什麼？</t>
+  </si>
+  <si>
+    <t>減少影像大小</t>
+  </si>
+  <si>
+    <t>壓縮影像檔案</t>
+  </si>
+  <si>
+    <t>改變影像顏色</t>
+  </si>
+  <si>
+    <t>提高影像對比度</t>
+  </si>
+  <si>
+    <t>對於8位元影像，灰度等級的總數 L 為何？</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>512</t>
+  </si>
+  <si>
+    <t>在灰度直方圖中，h(k) = nk 代表什麼意義？</t>
+  </si>
+  <si>
+    <t>第 k 個灰度級的機率</t>
+  </si>
+  <si>
+    <t>第 k 個灰度級的標準差</t>
+  </si>
+  <si>
+    <t>第 k 個灰度級的平均值</t>
+  </si>
+  <si>
+    <t>第 k 個灰度級的像素數量</t>
+  </si>
+  <si>
+    <t>在灰度直方圖中，p(k) = nk / N 代表什麼意義？</t>
+  </si>
+  <si>
+    <t>第 k 個灰度級的變異數</t>
+  </si>
+  <si>
+    <t>第 k 個灰度級的累積分布</t>
+  </si>
+  <si>
+    <t>第 k 個灰度級出現的機率</t>
+  </si>
+  <si>
+    <t>灰度線性變換可以將某一範圍的像素值映射到另一範圍，例如將 [100, 150] 映射到什麼範圍最常見？</t>
+  </si>
+  <si>
+    <t>[0, 100]</t>
+  </si>
+  <si>
+    <t>[50, 200]</t>
+  </si>
+  <si>
+    <t>[0, 255]</t>
+  </si>
+  <si>
+    <t>[100, 255]</t>
+  </si>
+  <si>
+    <t>在灰度線性變換 s = a × p + b 中，參數 a 和 b 的值如何決定？</t>
+  </si>
+  <si>
+    <t>固定為 1 和 0</t>
+  </si>
+  <si>
+    <t>根據影像大小決定</t>
+  </si>
+  <si>
+    <t>基於用戶需求或應用來定義</t>
+  </si>
+  <si>
+    <t>由系統自動計算</t>
+  </si>
+  <si>
+    <t>灰度對數變換的數學表達式為 s = c × log(1 + r)，其中 c 的作用是什麼？</t>
+  </si>
+  <si>
+    <t>決定影像大小</t>
+  </si>
+  <si>
+    <t>設定影像格式</t>
+  </si>
+  <si>
+    <t>控制影像顏色</t>
+  </si>
+  <si>
+    <t>調整輸出的影像強弱</t>
+  </si>
+  <si>
+    <t>在灰度對數變換中，當 r = 0 時，對數變換的值為何？</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>未定義</t>
+  </si>
+  <si>
+    <t>無窮大</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>在灰度對數變換中，隨著 r 的增加，對數值的增長速度會如何變化？</t>
+  </si>
+  <si>
+    <t>逐漸加快</t>
+  </si>
+  <si>
+    <t>保持不變</t>
+  </si>
+  <si>
+    <t>逐漸減慢</t>
+  </si>
+  <si>
+    <t>先快後慢再快</t>
+  </si>
+  <si>
+    <t>在灰度對數變換中，暗部（低灰階值）的變化相較於亮部（高灰階值）的變化如何？</t>
+  </si>
+  <si>
+    <t>變化較小</t>
+  </si>
+  <si>
+    <t>變化相同</t>
+  </si>
+  <si>
+    <t>變化更為劇烈</t>
+  </si>
+  <si>
+    <t>沒有變化</t>
+  </si>
+  <si>
+    <t>直方圖標準化通常將影像的灰度範圍映射到什麼目標範圍？</t>
+  </si>
+  <si>
+    <t>[1, 256]</t>
+  </si>
+  <si>
+    <t>[0, 128]</t>
+  </si>
+  <si>
+    <t>在直方圖標準化的公式中，rmin 和 rmax 分別代表什麼？</t>
+  </si>
+  <si>
+    <t>影像的平均值和標準差</t>
+  </si>
+  <si>
+    <t>影像的對比度範圍</t>
+  </si>
+  <si>
+    <t>影像的寬度和高度</t>
+  </si>
+  <si>
+    <t>影像的最小和最大灰度值</t>
+  </si>
+  <si>
+    <t>直方圖標準化可以解決影像的什麼問題？</t>
+  </si>
+  <si>
+    <t>影像顏色失真</t>
+  </si>
+  <si>
+    <t>影像噪點過多</t>
+  </si>
+  <si>
+    <t>僅使用部分灰度範圍導致對比度降低</t>
+  </si>
+  <si>
+    <t>像素儲存了該位置的什麼資訊？</t>
+  </si>
+  <si>
+    <t>時間資訊</t>
+  </si>
+  <si>
+    <t>格式資訊</t>
+  </si>
+  <si>
+    <t>位置資訊</t>
+  </si>
+  <si>
+    <t>強度資訊</t>
+  </si>
+  <si>
+    <t>在數位影像處理領域中，像素變換佔有什麼樣的位置？</t>
+  </si>
+  <si>
+    <t>次要的位置</t>
+  </si>
+  <si>
+    <t>重要的位置</t>
+  </si>
+  <si>
+    <t>可有可無的位置</t>
+  </si>
+  <si>
+    <t>過時的位置</t>
+  </si>
+  <si>
+    <t>灰度線性變換是基於對影像中每個像素值進行什麼操作的觀念？</t>
+  </si>
+  <si>
+    <t>非線性縮放</t>
+  </si>
+  <si>
+    <t>線性縮放</t>
+  </si>
+  <si>
+    <t>隨機變換</t>
+  </si>
+  <si>
+    <t>固定映射</t>
+  </si>
+  <si>
+    <t>在 RGB 彩色影像中，三個分量矩陣分別代表什麼？</t>
+  </si>
+  <si>
+    <t>亮度、對比度、飽和度</t>
+  </si>
+  <si>
+    <t>紅色、綠色、藍色的分量</t>
+  </si>
+  <si>
+    <t>長度、寬度、高度</t>
+  </si>
+  <si>
+    <t>X、Y、Z 座標</t>
+  </si>
+  <si>
+    <t>灰度對數變換在什麼領域的影像中特別有效？</t>
+  </si>
+  <si>
+    <t>需要增強暗部細節的特定領域</t>
+  </si>
+  <si>
+    <t>需要壓縮檔案的領域</t>
+  </si>
+  <si>
+    <t>需要改變顏色的領域</t>
+  </si>
+  <si>
+    <t>需要放大影像的領域</t>
+  </si>
+  <si>
+    <t>直方圖標準化後，影像可以更好地利用什麼？</t>
+  </si>
+  <si>
+    <t>儲存空間</t>
+  </si>
+  <si>
+    <t>整個灰度範圍</t>
+  </si>
+  <si>
+    <t>處理時間</t>
+  </si>
+  <si>
+    <t>記憶體資源</t>
+  </si>
+  <si>
+    <t>在直方圖標準化的公式 s = (r - rmin) / (rmax - rmin) × (L - 1) 中，L 代表什麼？</t>
+  </si>
+  <si>
+    <t>影像的長度</t>
+  </si>
+  <si>
+    <t>影像的寬度</t>
+  </si>
+  <si>
+    <t>灰度等級的總數</t>
+  </si>
+  <si>
+    <t>像素的總數</t>
+  </si>
+  <si>
+    <t>灰度線性變換屬於什麼類型的影像處理方法？</t>
+  </si>
+  <si>
+    <t>複雜且少用</t>
+  </si>
+  <si>
+    <t>簡單且常用</t>
+  </si>
+  <si>
+    <t>過時且淘汰</t>
+  </si>
+  <si>
+    <t>實驗性質</t>
+  </si>
+  <si>
+    <t>在灰度對數變換中，減少高強度的重要性意味著什麼？</t>
+  </si>
+  <si>
+    <t>完全忽略高強度區域</t>
+  </si>
+  <si>
+    <t>降低亮部的變化幅度</t>
+  </si>
+  <si>
+    <t>增加亮部的對比度</t>
+  </si>
+  <si>
+    <t>移除亮部像素</t>
+  </si>
+  <si>
+    <t>若要將灰度範圍 [50, 200] 的影像標準化到 [0, 255]，根據直方圖標準化公式，當原始像素值 r = 125 時，標準化後的像素值 s 最接近多少？</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>在灰度線性變換中，若要將 [100, 150] 映射到 [0, 255]，參數 a 的值應該為多少？</t>
+  </si>
+  <si>
+    <t>1.7</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>2.55</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>灰度對數變換相較於線性變換，在處理動態範圍較大的影像時有什麼優勢？</t>
+  </si>
+  <si>
+    <t>處理速度更快</t>
+  </si>
+  <si>
+    <t>能更好地壓縮高動態範圍，同時保留暗部細節</t>
+  </si>
+  <si>
+    <t>佔用記憶體更少</t>
+  </si>
+  <si>
+    <t>不需要額外參數</t>
+  </si>
+  <si>
+    <t>在直方圖標準化過程中，如果影像的 rmin = rmax，會發生什麼情況？</t>
+  </si>
+  <si>
+    <t>標準化正常進行</t>
+  </si>
+  <si>
+    <t>會產生除以零的錯誤</t>
+  </si>
+  <si>
+    <t>影像變成全黑</t>
+  </si>
+  <si>
+    <t>影像變成全白</t>
+  </si>
+  <si>
+    <t>若一張影像經過灰度線性變換 s = 2p + 30，其中 p 的範圍是 [0, 100]，則輸出 s 的範圍為何？</t>
+  </si>
+  <si>
+    <t>[0, 200]</t>
+  </si>
+  <si>
+    <t>[30, 230]</t>
+  </si>
+  <si>
+    <t>[0, 230]</t>
+  </si>
+  <si>
+    <t>[30, 255]</t>
+  </si>
+  <si>
+    <t>在灰度對數變換 s = c × log(1 + r) 中，若要使輸出範圍達到 [0, 255]，當 r 的最大值為 255 時，c 的值應如何設定？</t>
+  </si>
+  <si>
+    <t>c = 1</t>
+  </si>
+  <si>
+    <t>c = 255</t>
+  </si>
+  <si>
+    <t>c = 255 / log(256)</t>
+  </si>
+  <si>
+    <t>c = log(256)</t>
+  </si>
+  <si>
+    <t>直方圖標準化和直方圖等化（Histogram Equalization）的主要差異在於什麼？</t>
+  </si>
+  <si>
+    <t>標準化只改變範圍，等化還會改變分布</t>
+  </si>
+  <si>
+    <t>兩者完全相同</t>
+  </si>
+  <si>
+    <t>等化只改變範圍，標準化改變分布</t>
+  </si>
+  <si>
+    <t>標準化用於彩色影像，等化用於灰階影像</t>
+  </si>
+  <si>
+    <t>在實際應用中，灰度線性變換的參數 a 和 b 通常如何選擇才能達到最佳對比度增強效果？</t>
+  </si>
+  <si>
+    <t>固定使用 a=2, b=0</t>
+  </si>
+  <si>
+    <t>根據影像的灰度分布統計特性來決定</t>
+  </si>
+  <si>
+    <t>使用預設值 a=1, b=1</t>
+  </si>
+  <si>
+    <t>若對一張影像先進行灰度對數變換，再進行直方圖標準化，這兩個操作的順序是否可以互換而得到相同結果？</t>
+  </si>
+  <si>
+    <t>可以，結果完全相同</t>
+  </si>
+  <si>
+    <t>不可以，順序會影響最終結果</t>
+  </si>
+  <si>
+    <t>只有在特定條件下可以</t>
+  </si>
+  <si>
+    <t>取決於影像的大小</t>
+  </si>
+  <si>
+    <t>在數位影像處理中，像素變換屬於哪一類處理方法？</t>
+  </si>
+  <si>
+    <t>頻率域處理</t>
+  </si>
+  <si>
+    <t>空間域處理</t>
+  </si>
+  <si>
+    <t>時間域處理</t>
+  </si>
+  <si>
+    <t>統計域處理</t>
+  </si>
+  <si>
+    <t>CH 04-影像的像素變換</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1035,19 +1101,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="74.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.75" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>213</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>214</v>
+        <v>8</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
@@ -1072,19 +1146,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1092,39 +1166,39 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -1132,239 +1206,239 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" t="s">
         <v>67</v>
       </c>
-      <c r="C16" t="s">
-        <v>68</v>
-      </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" t="s">
         <v>70</v>
-      </c>
-      <c r="C17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" t="s">
-        <v>67</v>
       </c>
       <c r="F17">
         <v>4</v>
@@ -1375,36 +1449,36 @@
         <v>73</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E18" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" t="s">
         <v>77</v>
       </c>
-      <c r="B19" t="s">
+      <c r="E19" t="s">
         <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" t="s">
-        <v>80</v>
-      </c>
-      <c r="E19" t="s">
-        <v>81</v>
       </c>
       <c r="F19">
         <v>4</v>
@@ -1412,59 +1486,59 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" t="s">
         <v>82</v>
       </c>
-      <c r="B20" t="s">
+      <c r="E20" t="s">
         <v>83</v>
       </c>
-      <c r="C20" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" t="s">
-        <v>85</v>
-      </c>
-      <c r="E20" t="s">
-        <v>86</v>
-      </c>
       <c r="F20">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" t="s">
         <v>87</v>
       </c>
-      <c r="B21" t="s">
+      <c r="E21" t="s">
         <v>88</v>
       </c>
-      <c r="C21" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21" t="s">
-        <v>48</v>
-      </c>
       <c r="F21">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" t="s">
         <v>91</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D22" t="s">
         <v>92</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22" t="s">
         <v>93</v>
-      </c>
-      <c r="D22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E22" t="s">
-        <v>48</v>
       </c>
       <c r="F22">
         <v>3</v>
@@ -1472,179 +1546,179 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" t="s">
         <v>95</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>96</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>97</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>98</v>
       </c>
-      <c r="E23" t="s">
-        <v>99</v>
-      </c>
       <c r="F23">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" t="s">
         <v>100</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D24" t="s">
         <v>101</v>
       </c>
-      <c r="C24" t="s">
+      <c r="E24" t="s">
         <v>102</v>
       </c>
-      <c r="D24" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" t="s">
-        <v>104</v>
-      </c>
       <c r="F24">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" t="s">
         <v>105</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" t="s">
         <v>106</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E25" t="s">
         <v>107</v>
       </c>
-      <c r="D25" t="s">
-        <v>108</v>
-      </c>
-      <c r="E25" t="s">
-        <v>109</v>
-      </c>
       <c r="F25">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" t="s">
         <v>110</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D26" t="s">
         <v>111</v>
       </c>
-      <c r="C26" t="s">
+      <c r="E26" t="s">
         <v>112</v>
       </c>
-      <c r="D26" t="s">
-        <v>113</v>
-      </c>
-      <c r="E26" t="s">
-        <v>114</v>
-      </c>
       <c r="F26">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" t="s">
         <v>115</v>
       </c>
-      <c r="B27" t="s">
+      <c r="D27" t="s">
         <v>116</v>
       </c>
-      <c r="C27" t="s">
+      <c r="E27" t="s">
         <v>117</v>
       </c>
-      <c r="D27" t="s">
-        <v>118</v>
-      </c>
-      <c r="E27" t="s">
-        <v>119</v>
-      </c>
       <c r="F27">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
+        <v>118</v>
+      </c>
+      <c r="B28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" t="s">
         <v>120</v>
       </c>
-      <c r="B28" t="s">
+      <c r="D28" t="s">
         <v>121</v>
       </c>
-      <c r="C28" t="s">
+      <c r="E28" t="s">
         <v>122</v>
       </c>
-      <c r="D28" t="s">
-        <v>123</v>
-      </c>
-      <c r="E28" t="s">
-        <v>124</v>
-      </c>
       <c r="F28">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
+        <v>123</v>
+      </c>
+      <c r="B29" t="s">
+        <v>124</v>
+      </c>
+      <c r="C29" t="s">
         <v>125</v>
       </c>
-      <c r="B29" t="s">
+      <c r="D29" t="s">
         <v>126</v>
       </c>
-      <c r="C29" t="s">
+      <c r="E29" t="s">
         <v>127</v>
       </c>
-      <c r="D29" t="s">
-        <v>128</v>
-      </c>
-      <c r="E29" t="s">
-        <v>129</v>
-      </c>
       <c r="F29">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" t="s">
         <v>130</v>
       </c>
-      <c r="B30" t="s">
+      <c r="D30" t="s">
         <v>131</v>
       </c>
-      <c r="C30" t="s">
-        <v>127</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>132</v>
       </c>
-      <c r="E30" t="s">
-        <v>133</v>
-      </c>
       <c r="F30">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
+        <v>133</v>
+      </c>
+      <c r="B31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" t="s">
         <v>134</v>
       </c>
-      <c r="B31" t="s">
+      <c r="D31" t="s">
+        <v>106</v>
+      </c>
+      <c r="E31" t="s">
         <v>135</v>
-      </c>
-      <c r="C31" t="s">
-        <v>136</v>
-      </c>
-      <c r="D31" t="s">
-        <v>137</v>
-      </c>
-      <c r="E31" t="s">
-        <v>138</v>
       </c>
       <c r="F31">
         <v>3</v>
@@ -1652,59 +1726,59 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
+        <v>136</v>
+      </c>
+      <c r="B32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" t="s">
+        <v>138</v>
+      </c>
+      <c r="D32" t="s">
         <v>139</v>
       </c>
-      <c r="B32" t="s">
+      <c r="E32" t="s">
         <v>140</v>
       </c>
-      <c r="C32" t="s">
-        <v>141</v>
-      </c>
-      <c r="D32" t="s">
-        <v>142</v>
-      </c>
-      <c r="E32" t="s">
-        <v>143</v>
-      </c>
       <c r="F32">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
+        <v>141</v>
+      </c>
+      <c r="B33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" t="s">
+        <v>142</v>
+      </c>
+      <c r="D33" t="s">
+        <v>143</v>
+      </c>
+      <c r="E33" t="s">
         <v>144</v>
       </c>
-      <c r="B33" t="s">
-        <v>131</v>
-      </c>
-      <c r="C33" t="s">
-        <v>127</v>
-      </c>
-      <c r="D33" t="s">
-        <v>132</v>
-      </c>
-      <c r="E33" t="s">
-        <v>145</v>
-      </c>
       <c r="F33">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
+        <v>145</v>
+      </c>
+      <c r="B34" t="s">
         <v>146</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>147</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>148</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>149</v>
-      </c>
-      <c r="E34" t="s">
-        <v>150</v>
       </c>
       <c r="F34">
         <v>4</v>
@@ -1712,36 +1786,36 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
+        <v>150</v>
+      </c>
+      <c r="B35" t="s">
         <v>151</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>152</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>153</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>154</v>
       </c>
-      <c r="E35" t="s">
-        <v>155</v>
-      </c>
       <c r="F35">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
+        <v>155</v>
+      </c>
+      <c r="B36" t="s">
         <v>156</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>157</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>158</v>
-      </c>
-      <c r="D36" t="s">
-        <v>24</v>
       </c>
       <c r="E36" t="s">
         <v>159</v>
@@ -1787,7 +1861,7 @@
         <v>169</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
@@ -1795,196 +1869,196 @@
         <v>170</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>171</v>
       </c>
       <c r="C39" t="s">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="D39" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E39" t="s">
-        <v>85</v>
+        <v>174</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>176</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>177</v>
       </c>
       <c r="D40" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E40" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B41" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C41" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D41" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E41" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>186</v>
       </c>
       <c r="C42" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D42" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E42" t="s">
-        <v>47</v>
+        <v>189</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B43" t="s">
-        <v>48</v>
+        <v>191</v>
       </c>
       <c r="C43" t="s">
-        <v>182</v>
+        <v>90</v>
       </c>
       <c r="D43" t="s">
-        <v>184</v>
+        <v>91</v>
       </c>
       <c r="E43" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B44" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="C44" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="D44" t="s">
-        <v>76</v>
+        <v>196</v>
       </c>
       <c r="E44" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B45" t="s">
-        <v>48</v>
+        <v>199</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>200</v>
       </c>
       <c r="D45" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="E45" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="B46" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
+        <v>205</v>
       </c>
       <c r="D46" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="E46" t="s">
-        <v>88</v>
+        <v>207</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="B47" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="C47" t="s">
-        <v>94</v>
+        <v>210</v>
       </c>
       <c r="D47" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="E47" t="s">
-        <v>48</v>
+        <v>212</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>214</v>
       </c>
       <c r="C48" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="D48" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="E48" t="s">
-        <v>88</v>
+        <v>217</v>
       </c>
       <c r="F48">
         <v>3</v>
@@ -1992,39 +2066,39 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>219</v>
       </c>
       <c r="C49" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="D49" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="E49" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="B50" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="C50" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="D50" t="s">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="E50" t="s">
-        <v>48</v>
+        <v>226</v>
       </c>
       <c r="F50">
         <v>2</v>
@@ -2032,42 +2106,42 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="B51" t="s">
-        <v>90</v>
+        <v>228</v>
       </c>
       <c r="C51" t="s">
-        <v>92</v>
+        <v>229</v>
       </c>
       <c r="D51" t="s">
-        <v>48</v>
+        <v>230</v>
       </c>
       <c r="E51" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="B52" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="C52" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="D52" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="E52" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="F52">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
